--- a/public/downloads/clientes-modelo.xlsx
+++ b/public/downloads/clientes-modelo.xlsx
@@ -397,69 +397,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:N3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Nome da Empresa</v>
+        <v>Nome Fantasia</v>
       </c>
       <c r="B1" t="str">
-        <v>CNPJ</v>
+        <v>Razão Social</v>
       </c>
       <c r="C1" t="str">
-        <v>Domínio da Empresa</v>
+        <v>CPF/CNPJ</v>
       </c>
       <c r="D1" t="str">
+        <v>IE</v>
+      </c>
+      <c r="E1" t="str">
+        <v>IM</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Contatos (Separado por '{}')</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Rua</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Número</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Bairro</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Complemento</v>
+      </c>
+      <c r="K1" t="str">
+        <v>CEP</v>
+      </c>
+      <c r="L1" t="str">
         <v>Cidade</v>
       </c>
-      <c r="E1" t="str">
+      <c r="M1" t="str">
         <v>Estado</v>
       </c>
-      <c r="F1" t="str">
-        <v>Nome do Contato</v>
-      </c>
-      <c r="G1" t="str">
-        <v>E-mail do Contato</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Telefone do Contato</v>
+      <c r="N1" t="str">
+        <v>Status</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Empresa Exemplo</v>
+      </c>
+      <c r="B2" t="str">
         <v>Empresa Exemplo Ltda</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>12.345.678/0001-95</v>
       </c>
-      <c r="C2" t="str">
-        <v>empresaexemplo.com.br</v>
-      </c>
       <c r="D2" t="str">
+        <v>123.456.789.110</v>
+      </c>
+      <c r="E2" t="str">
+        <v>987654</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Maria Silva;maria.silva@empresaexemplo.com.br;+5511999999999{}João Souza;joao.souza@empresaexemplo.com.br;+5511988888888</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Rua das Flores</v>
+      </c>
+      <c r="H2" t="str">
+        <v>100</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Centro</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Sala 2</v>
+      </c>
+      <c r="K2" t="str">
+        <v>01310-100</v>
+      </c>
+      <c r="L2" t="str">
         <v>São Paulo</v>
       </c>
-      <c r="E2" t="str">
+      <c r="M2" t="str">
         <v>SP</v>
       </c>
-      <c r="F2" t="str">
-        <v>Maria Silva</v>
-      </c>
-      <c r="G2" t="str">
-        <v>maria.silva@empresaexemplo.com.br</v>
-      </c>
-      <c r="H2" t="str">
-        <v>+5511999999999</v>
+      <c r="N2" t="str">
+        <v>Ativo</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>Ana Pereira</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>111.444.777-35</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -468,18 +504,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>João Souza</v>
+        <v>Ana Pereira;ana.pereira@gmail.com;+5511977777777</v>
       </c>
       <c r="G3" t="str">
-        <v>joao.souza@gmail.com</v>
+        <v>Av. Paulista</v>
       </c>
       <c r="H3" t="str">
-        <v>+5511988888888</v>
+        <v>900</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Bela Vista</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>01310-200</v>
+      </c>
+      <c r="L3" t="str">
+        <v>São Paulo</v>
+      </c>
+      <c r="M3" t="str">
+        <v>SP</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Ativo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/downloads/clientes-modelo.xlsx
+++ b/public/downloads/clientes-modelo.xlsx
@@ -416,7 +416,7 @@
         <v>IM</v>
       </c>
       <c r="F1" t="str">
-        <v>Contatos (Separado por '{}')</v>
+        <v>Contatos (formato: {ID, Nome, E-mail, Telefone, Setor})</v>
       </c>
       <c r="G1" t="str">
         <v>Rua</v>
@@ -460,7 +460,7 @@
         <v>987654</v>
       </c>
       <c r="F2" t="str">
-        <v>Maria Silva;maria.silva@empresaexemplo.com.br;+5511999999999{}João Souza;joao.souza@empresaexemplo.com.br;+5511988888888</v>
+        <v>{1294494, Maria Silva, maria.silva@empresaexemplo.com.br, 5511999999999, Comercial};{1294495, João Souza, joao.souza@empresaexemplo.com.br, 5511988888888, Financeiro}</v>
       </c>
       <c r="G2" t="str">
         <v>Rua das Flores</v>
@@ -504,7 +504,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Ana Pereira;ana.pereira@gmail.com;+5511977777777</v>
+        <v>{1294496, Ana Pereira, ana.pereira@gmail.com, 5511977777777, Diretoria}</v>
       </c>
       <c r="G3" t="str">
         <v>Av. Paulista</v>
